--- a/output/2025_estado_nutricional_por_comuna.xlsx
+++ b/output/2025_estado_nutricional_por_comuna.xlsx
@@ -448,16 +448,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -473,7 +465,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -481,30 +473,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -803,276 +777,276 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:89">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" t="s">
         <v>51</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" t="s">
         <v>54</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" t="s">
         <v>55</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BF1" t="s">
         <v>56</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" t="s">
         <v>57</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" t="s">
         <v>58</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" t="s">
         <v>59</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" t="s">
         <v>60</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" t="s">
         <v>61</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" t="s">
         <v>62</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" t="s">
         <v>63</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" t="s">
         <v>64</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BO1" t="s">
         <v>65</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BP1" t="s">
         <v>66</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" t="s">
         <v>67</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BR1" t="s">
         <v>68</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BS1" t="s">
         <v>69</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BT1" t="s">
         <v>70</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BU1" t="s">
         <v>71</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BV1" t="s">
         <v>72</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BW1" t="s">
         <v>73</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BX1" t="s">
         <v>74</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BY1" t="s">
         <v>75</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="BZ1" t="s">
         <v>76</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CA1" t="s">
         <v>77</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CB1" t="s">
         <v>78</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CC1" t="s">
         <v>79</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CD1" t="s">
         <v>80</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CE1" t="s">
         <v>81</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CF1" t="s">
         <v>82</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CG1" t="s">
         <v>83</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CH1" t="s">
         <v>84</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CI1" t="s">
         <v>85</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CJ1" t="s">
         <v>86</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CK1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:89">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -1284,41 +1258,41 @@
       </c>
     </row>
     <row r="3" spans="1:89">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
-        <v>3199</v>
+        <v>2983</v>
       </c>
       <c r="C3">
-        <v>1901</v>
+        <v>1761</v>
       </c>
       <c r="D3">
-        <v>0.594248202563301</v>
+        <v>0.5903452899765337</v>
       </c>
       <c r="E3">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F3">
-        <v>0.0665833072835261</v>
+        <v>0.06738183037210861</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H3">
-        <v>0.01875586120662707</v>
+        <v>0.01944351324170298</v>
       </c>
       <c r="I3">
-        <v>695</v>
+        <v>648</v>
       </c>
       <c r="J3">
-        <v>0.2172553923100969</v>
+        <v>0.2172309755279919</v>
       </c>
       <c r="K3">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="L3">
-        <v>0.08471397311659894</v>
+        <v>0.08447871270533021</v>
       </c>
       <c r="M3">
         <v>1272</v>
@@ -1387,37 +1361,37 @@
         <v>0.2179091310101456</v>
       </c>
       <c r="AI3">
-        <v>4471</v>
+        <v>4255</v>
       </c>
       <c r="AJ3">
-        <v>2649</v>
+        <v>2509</v>
       </c>
       <c r="AK3">
-        <v>0.5924849027063297</v>
+        <v>0.5896592244418332</v>
       </c>
       <c r="AL3">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AM3">
-        <v>0.06441511966003131</v>
+        <v>0.06486486486486487</v>
       </c>
       <c r="AN3">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AO3">
-        <v>0.01766942518452248</v>
+        <v>0.01809635722679201</v>
       </c>
       <c r="AP3">
-        <v>949</v>
+        <v>902</v>
       </c>
       <c r="AQ3">
-        <v>0.2122567658242004</v>
+        <v>0.2119858989424207</v>
       </c>
       <c r="AR3">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="AS3">
-        <v>0.09885931558935361</v>
+        <v>0.09941245593419507</v>
       </c>
       <c r="AT3">
         <v>357</v>
@@ -1508,7 +1482,7 @@
       </c>
     </row>
     <row r="4" spans="1:89">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -1644,31 +1618,31 @@
         <v>0.1396825396825397</v>
       </c>
       <c r="AT4">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AU4">
         <v>17</v>
       </c>
       <c r="AV4">
-        <v>0.217948717948718</v>
+        <v>0.2207792207792208</v>
       </c>
       <c r="AW4">
         <v>2</v>
       </c>
       <c r="AX4">
-        <v>0.02564102564102564</v>
+        <v>0.02597402597402598</v>
       </c>
       <c r="BA4">
         <v>17</v>
       </c>
       <c r="BB4">
-        <v>0.217948717948718</v>
+        <v>0.2207792207792208</v>
       </c>
       <c r="BC4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="BD4">
-        <v>0.5384615384615384</v>
+        <v>0.5324675324675324</v>
       </c>
       <c r="BP4">
         <v>1356</v>
@@ -1732,7 +1706,7 @@
       </c>
     </row>
     <row r="5" spans="1:89">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -1956,7 +1930,7 @@
       </c>
     </row>
     <row r="6" spans="1:89">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -2201,7 +2175,7 @@
       </c>
     </row>
     <row r="7" spans="1:89">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -2452,7 +2426,7 @@
       </c>
     </row>
     <row r="8" spans="1:89">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -2703,7 +2677,7 @@
       </c>
     </row>
     <row r="9" spans="1:89">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -2936,7 +2910,7 @@
       </c>
     </row>
     <row r="10" spans="1:89">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -3181,7 +3155,7 @@
       </c>
     </row>
     <row r="11" spans="1:89">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -3405,7 +3379,7 @@
       </c>
     </row>
     <row r="12" spans="1:89">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -3650,7 +3624,7 @@
       </c>
     </row>
     <row r="13" spans="1:89">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -3901,7 +3875,7 @@
       </c>
     </row>
     <row r="14" spans="1:89">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -4146,7 +4120,7 @@
       </c>
     </row>
     <row r="15" spans="1:89">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -4364,7 +4338,7 @@
       </c>
     </row>
     <row r="16" spans="1:89">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -4609,7 +4583,7 @@
       </c>
     </row>
     <row r="17" spans="1:89">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -4854,252 +4828,246 @@
       </c>
     </row>
     <row r="18" spans="1:89">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>3068</v>
+        <v>2473</v>
       </c>
       <c r="C18">
-        <v>1878</v>
+        <v>1497</v>
       </c>
       <c r="D18">
-        <v>0.6121251629726207</v>
+        <v>0.6053376465830974</v>
       </c>
       <c r="E18">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="F18">
-        <v>0.04595827900912647</v>
+        <v>0.04771532551556813</v>
       </c>
       <c r="G18">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H18">
-        <v>0.005541069100391135</v>
+        <v>0.003234937323089365</v>
       </c>
       <c r="I18">
-        <v>699</v>
+        <v>567</v>
       </c>
       <c r="J18">
-        <v>0.2278357235984355</v>
+        <v>0.2292761827739588</v>
       </c>
       <c r="K18">
-        <v>333</v>
+        <v>283</v>
       </c>
       <c r="L18">
-        <v>0.1085397653194263</v>
+        <v>0.1144359078042863</v>
       </c>
       <c r="M18">
-        <v>1584</v>
+        <v>1248</v>
       </c>
       <c r="N18">
-        <v>841</v>
+        <v>633</v>
       </c>
       <c r="O18">
-        <v>0.5309343434343434</v>
+        <v>0.5072115384615384</v>
       </c>
       <c r="P18">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="Q18">
-        <v>0.04924242424242424</v>
+        <v>0.04086538461538462</v>
       </c>
       <c r="R18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>0.006313131313131313</v>
+        <v>0.005608974358974359</v>
       </c>
       <c r="T18">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="U18">
-        <v>0.2215909090909091</v>
+        <v>0.2371794871794872</v>
       </c>
       <c r="V18">
-        <v>304</v>
+        <v>261</v>
       </c>
       <c r="W18">
-        <v>0.1919191919191919</v>
+        <v>0.2091346153846154</v>
       </c>
       <c r="X18">
-        <v>3048</v>
+        <v>2438</v>
       </c>
       <c r="Y18">
-        <v>1488</v>
+        <v>1142</v>
       </c>
       <c r="Z18">
-        <v>0.4881889763779528</v>
+        <v>0.4684167350287121</v>
       </c>
       <c r="AA18">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="AB18">
-        <v>0.04461942257217848</v>
+        <v>0.04142739950779328</v>
       </c>
       <c r="AC18">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AD18">
-        <v>0.006233595800524934</v>
+        <v>0.005742411812961444</v>
       </c>
       <c r="AE18">
-        <v>614</v>
+        <v>511</v>
       </c>
       <c r="AF18">
-        <v>0.2014435695538058</v>
+        <v>0.2095980311730927</v>
       </c>
       <c r="AG18">
-        <v>791</v>
+        <v>670</v>
       </c>
       <c r="AH18">
-        <v>0.2595144356955381</v>
+        <v>0.2748154224774405</v>
       </c>
       <c r="AI18">
-        <v>4652</v>
+        <v>3721</v>
       </c>
       <c r="AJ18">
-        <v>2719</v>
+        <v>2130</v>
       </c>
       <c r="AK18">
-        <v>0.5844797936371453</v>
+        <v>0.5724267669981188</v>
       </c>
       <c r="AL18">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="AM18">
-        <v>0.04707652622527945</v>
+        <v>0.04541789841440473</v>
       </c>
       <c r="AN18">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="AO18">
-        <v>0.005803955288048152</v>
+        <v>0.00403117441547971</v>
       </c>
       <c r="AP18">
-        <v>1050</v>
+        <v>863</v>
       </c>
       <c r="AQ18">
-        <v>0.2257093723129837</v>
+        <v>0.2319269013705993</v>
       </c>
       <c r="AR18">
-        <v>637</v>
+        <v>544</v>
       </c>
       <c r="AS18">
-        <v>0.1369303525365434</v>
+        <v>0.1461972588013975</v>
       </c>
       <c r="AT18">
-        <v>512</v>
+        <v>428</v>
       </c>
       <c r="AU18">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AV18">
-        <v>0.1953125</v>
+        <v>0.1892523364485981</v>
       </c>
       <c r="AW18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX18">
-        <v>0.017578125</v>
+        <v>0.01635514018691589</v>
       </c>
       <c r="BA18">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="BB18">
-        <v>0.330078125</v>
+        <v>0.338785046728972</v>
       </c>
       <c r="BC18">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="BD18">
-        <v>0.45703125</v>
+        <v>0.455607476635514</v>
       </c>
       <c r="BE18">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BF18">
         <v>2</v>
       </c>
       <c r="BG18">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="BL18">
+        <v>0.5</v>
+      </c>
+      <c r="BN18">
         <v>2</v>
       </c>
-      <c r="BM18">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="BN18">
-        <v>8</v>
-      </c>
       <c r="BO18">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="BP18">
-        <v>7257</v>
+        <v>4996</v>
       </c>
       <c r="BQ18">
-        <v>2356</v>
+        <v>1589</v>
       </c>
       <c r="BR18">
-        <v>0.3246520600799228</v>
+        <v>0.3180544435548439</v>
       </c>
       <c r="BS18">
-        <v>678</v>
+        <v>398</v>
       </c>
       <c r="BT18">
-        <v>0.09342703596527491</v>
+        <v>0.07966373098478784</v>
       </c>
       <c r="BW18">
-        <v>2175</v>
+        <v>1520</v>
       </c>
       <c r="BX18">
-        <v>0.2997106242248863</v>
+        <v>0.3042433947157726</v>
       </c>
       <c r="BY18">
-        <v>2048</v>
+        <v>1489</v>
       </c>
       <c r="BZ18">
-        <v>0.282210279729916</v>
+        <v>0.2980384307445957</v>
       </c>
       <c r="CA18">
-        <v>3292</v>
+        <v>2597</v>
       </c>
       <c r="CB18">
-        <v>1440</v>
+        <v>1151</v>
       </c>
       <c r="CC18">
-        <v>0.4374240583232078</v>
+        <v>0.4432036965729688</v>
       </c>
       <c r="CD18">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="CE18">
-        <v>0.04434993924665857</v>
+        <v>0.04582210242587601</v>
       </c>
       <c r="CF18">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="CG18">
-        <v>0.005467800729040097</v>
+        <v>0.004235656526761648</v>
       </c>
       <c r="CH18">
-        <v>749</v>
+        <v>585</v>
       </c>
       <c r="CI18">
-        <v>0.2275212636695018</v>
+        <v>0.2252599152868695</v>
       </c>
       <c r="CJ18">
-        <v>939</v>
+        <v>731</v>
       </c>
       <c r="CK18">
-        <v>0.2852369380315917</v>
+        <v>0.2814786291875241</v>
       </c>
     </row>
     <row r="19" spans="1:89">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -5344,7 +5312,7 @@
       </c>
     </row>
     <row r="20" spans="1:89">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -5589,7 +5557,7 @@
       </c>
     </row>
     <row r="21" spans="1:89">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -5725,31 +5693,31 @@
         <v>0.1132416787264834</v>
       </c>
       <c r="AT21">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="AU21">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="AV21">
-        <v>0.277027027027027</v>
+        <v>0.2775510204081633</v>
       </c>
       <c r="AW21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX21">
-        <v>0.02027027027027027</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="BA21">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="BB21">
-        <v>0.2882882882882883</v>
+        <v>0.2918367346938776</v>
       </c>
       <c r="BC21">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="BD21">
-        <v>0.4144144144144144</v>
+        <v>0.410204081632653</v>
       </c>
       <c r="BE21">
         <v>126</v>
@@ -5779,68 +5747,68 @@
         <v>0.492063492063492</v>
       </c>
       <c r="BP21">
-        <v>3981</v>
+        <v>4290</v>
       </c>
       <c r="BQ21">
-        <v>1393</v>
+        <v>1499</v>
       </c>
       <c r="BR21">
-        <v>0.349912082391359</v>
+        <v>0.3494172494172494</v>
       </c>
       <c r="BS21">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="BT21">
-        <v>0.1019844260236122</v>
+        <v>0.103030303030303</v>
       </c>
       <c r="BW21">
-        <v>1161</v>
+        <v>1250</v>
       </c>
       <c r="BX21">
-        <v>0.2916352675207234</v>
+        <v>0.2913752913752914</v>
       </c>
       <c r="BY21">
-        <v>1021</v>
+        <v>1099</v>
       </c>
       <c r="BZ21">
-        <v>0.2564682240643055</v>
+        <v>0.2561771561771562</v>
       </c>
       <c r="CA21">
-        <v>2602</v>
+        <v>2841</v>
       </c>
       <c r="CB21">
-        <v>1149</v>
+        <v>1258</v>
       </c>
       <c r="CC21">
-        <v>0.4415833973866257</v>
+        <v>0.4428018303414291</v>
       </c>
       <c r="CD21">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="CE21">
-        <v>0.06302843966179862</v>
+        <v>0.05843013023583245</v>
       </c>
       <c r="CF21">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="CG21">
-        <v>0.02036894696387394</v>
+        <v>0.02111932418162619</v>
       </c>
       <c r="CH21">
-        <v>617</v>
+        <v>670</v>
       </c>
       <c r="CI21">
-        <v>0.2371252882398155</v>
+        <v>0.2358324533614924</v>
       </c>
       <c r="CJ21">
-        <v>619</v>
+        <v>687</v>
       </c>
       <c r="CK21">
-        <v>0.2378939277478862</v>
+        <v>0.2418162618796199</v>
       </c>
     </row>
     <row r="22" spans="1:89">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -6091,7 +6059,7 @@
       </c>
     </row>
     <row r="23" spans="1:89">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -6336,7 +6304,7 @@
       </c>
     </row>
     <row r="24" spans="1:89">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -6526,31 +6494,31 @@
         <v>0.432258064516129</v>
       </c>
       <c r="BP24">
-        <v>5294</v>
+        <v>5235</v>
       </c>
       <c r="BQ24">
-        <v>1779</v>
+        <v>1765</v>
       </c>
       <c r="BR24">
-        <v>0.3360408009066868</v>
+        <v>0.3371537726838587</v>
       </c>
       <c r="BS24">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="BT24">
-        <v>0.1023800528900642</v>
+        <v>0.1033428844317097</v>
       </c>
       <c r="BW24">
-        <v>1576</v>
+        <v>1543</v>
       </c>
       <c r="BX24">
-        <v>0.297695504344541</v>
+        <v>0.2947468958930277</v>
       </c>
       <c r="BY24">
-        <v>1397</v>
+        <v>1386</v>
       </c>
       <c r="BZ24">
-        <v>0.263883641858708</v>
+        <v>0.264756446991404</v>
       </c>
       <c r="CA24">
         <v>2205</v>
@@ -6587,7 +6555,7 @@
       </c>
     </row>
     <row r="25" spans="1:89">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -6838,7 +6806,7 @@
       </c>
     </row>
     <row r="26" spans="1:89">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -7077,7 +7045,7 @@
       </c>
     </row>
     <row r="27" spans="1:89">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -7328,7 +7296,7 @@
       </c>
     </row>
     <row r="28" spans="1:89">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -7540,7 +7508,7 @@
       </c>
     </row>
     <row r="29" spans="1:89">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -7791,7 +7759,7 @@
       </c>
     </row>
     <row r="30" spans="1:89">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -8042,7 +8010,7 @@
       </c>
     </row>
     <row r="31" spans="1:89">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -8281,7 +8249,7 @@
       </c>
     </row>
     <row r="32" spans="1:89">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -8526,7 +8494,7 @@
       </c>
     </row>
     <row r="33" spans="1:89">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -8771,7 +8739,7 @@
       </c>
     </row>
     <row r="34" spans="1:89">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -9022,7 +8990,7 @@
       </c>
     </row>
     <row r="35" spans="1:89">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -9240,7 +9208,7 @@
       </c>
     </row>
     <row r="36" spans="1:89">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -9485,7 +9453,7 @@
       </c>
     </row>
     <row r="37" spans="1:89">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -9730,7 +9698,7 @@
       </c>
     </row>
     <row r="38" spans="1:89">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -9866,58 +9834,58 @@
         <v>0.09774229074889867</v>
       </c>
       <c r="AT38">
-        <v>1955</v>
+        <v>1762</v>
       </c>
       <c r="AU38">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="AV38">
-        <v>0.2603580562659846</v>
+        <v>0.2678774120317821</v>
       </c>
       <c r="AW38">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AX38">
-        <v>0.01636828644501279</v>
+        <v>0.01532349602724177</v>
       </c>
       <c r="BA38">
-        <v>597</v>
+        <v>544</v>
       </c>
       <c r="BB38">
-        <v>0.3053708439897698</v>
+        <v>0.3087400681044268</v>
       </c>
       <c r="BC38">
-        <v>817</v>
+        <v>719</v>
       </c>
       <c r="BD38">
-        <v>0.4179028132992327</v>
+        <v>0.4080590238365494</v>
       </c>
       <c r="BE38">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="BF38">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="BG38">
-        <v>0.8372093023255814</v>
+        <v>0.8319327731092437</v>
       </c>
       <c r="BH38">
         <v>1</v>
       </c>
       <c r="BI38">
-        <v>0.007751937984496124</v>
+        <v>0.008403361344537815</v>
       </c>
       <c r="BL38">
         <v>11</v>
       </c>
       <c r="BM38">
-        <v>0.08527131782945736</v>
+        <v>0.09243697478991597</v>
       </c>
       <c r="BN38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BO38">
-        <v>0.06976744186046512</v>
+        <v>0.06722689075630252</v>
       </c>
       <c r="BP38">
         <v>14114</v>
@@ -9981,7 +9949,7 @@
       </c>
     </row>
     <row r="39" spans="1:89">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -10220,7 +10188,7 @@
       </c>
     </row>
     <row r="40" spans="1:89">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -10465,7 +10433,7 @@
       </c>
     </row>
     <row r="41" spans="1:89">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -10716,7 +10684,7 @@
       </c>
     </row>
     <row r="42" spans="1:89">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -10961,7 +10929,7 @@
       </c>
     </row>
     <row r="43" spans="1:89">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -11212,7 +11180,7 @@
       </c>
     </row>
     <row r="44" spans="1:89">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -11463,7 +11431,7 @@
       </c>
     </row>
     <row r="45" spans="1:89">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -11687,7 +11655,7 @@
       </c>
     </row>
     <row r="46" spans="1:89">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -11932,7 +11900,7 @@
       </c>
     </row>
     <row r="47" spans="1:89">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -12150,7 +12118,7 @@
       </c>
     </row>
     <row r="48" spans="1:89">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -12395,7 +12363,7 @@
       </c>
     </row>
     <row r="49" spans="1:89">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -12646,7 +12614,7 @@
       </c>
     </row>
     <row r="50" spans="1:89">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -12864,7 +12832,7 @@
       </c>
     </row>
     <row r="51" spans="1:89">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -13103,7 +13071,7 @@
       </c>
     </row>
     <row r="52" spans="1:89">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -13318,7 +13286,7 @@
       </c>
     </row>
     <row r="53" spans="1:89">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -13552,84 +13520,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>46</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>57</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>67</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>68</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>78</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -13697,17 +13665,17 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
-        <v>3199</v>
+        <v>2983</v>
       </c>
       <c r="C3">
-        <v>1901</v>
+        <v>1761</v>
       </c>
       <c r="D3">
-        <v>0.594248202563301</v>
+        <v>0.5903452899765337</v>
       </c>
       <c r="E3">
         <v>1272</v>
@@ -13728,13 +13696,13 @@
         <v>0.5050727834142038</v>
       </c>
       <c r="K3">
-        <v>4471</v>
+        <v>4255</v>
       </c>
       <c r="L3">
-        <v>2649</v>
+        <v>2509</v>
       </c>
       <c r="M3">
-        <v>0.5924849027063297</v>
+        <v>0.5896592244418332</v>
       </c>
       <c r="N3">
         <v>357</v>
@@ -13765,7 +13733,7 @@
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -13805,13 +13773,13 @@
         <v>0.5246031746031746</v>
       </c>
       <c r="N4">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O4">
         <v>17</v>
       </c>
       <c r="P4">
-        <v>0.217948717948718</v>
+        <v>0.2207792207792208</v>
       </c>
       <c r="T4">
         <v>1356</v>
@@ -13833,7 +13801,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -13901,7 +13869,7 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -13978,7 +13946,7 @@
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -14055,7 +14023,7 @@
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -14132,7 +14100,7 @@
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -14203,7 +14171,7 @@
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -14280,7 +14248,7 @@
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -14348,7 +14316,7 @@
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -14425,7 +14393,7 @@
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -14502,7 +14470,7 @@
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -14579,7 +14547,7 @@
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -14647,7 +14615,7 @@
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -14724,7 +14692,7 @@
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -14801,84 +14769,84 @@
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>3068</v>
+        <v>2473</v>
       </c>
       <c r="C18">
-        <v>1878</v>
+        <v>1497</v>
       </c>
       <c r="D18">
-        <v>0.6121251629726207</v>
+        <v>0.6053376465830974</v>
       </c>
       <c r="E18">
-        <v>1584</v>
+        <v>1248</v>
       </c>
       <c r="F18">
-        <v>841</v>
+        <v>633</v>
       </c>
       <c r="G18">
-        <v>0.5309343434343434</v>
+        <v>0.5072115384615384</v>
       </c>
       <c r="H18">
-        <v>3048</v>
+        <v>2438</v>
       </c>
       <c r="I18">
-        <v>1488</v>
+        <v>1142</v>
       </c>
       <c r="J18">
-        <v>0.4881889763779528</v>
+        <v>0.4684167350287121</v>
       </c>
       <c r="K18">
-        <v>4652</v>
+        <v>3721</v>
       </c>
       <c r="L18">
-        <v>2719</v>
+        <v>2130</v>
       </c>
       <c r="M18">
-        <v>0.5844797936371453</v>
+        <v>0.5724267669981188</v>
       </c>
       <c r="N18">
-        <v>512</v>
+        <v>428</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="P18">
-        <v>0.1953125</v>
+        <v>0.1892523364485981</v>
       </c>
       <c r="Q18">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R18">
         <v>2</v>
       </c>
       <c r="S18">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="T18">
-        <v>7257</v>
+        <v>4996</v>
       </c>
       <c r="U18">
-        <v>2356</v>
+        <v>1589</v>
       </c>
       <c r="V18">
-        <v>0.3246520600799228</v>
+        <v>0.3180544435548439</v>
       </c>
       <c r="W18">
-        <v>3292</v>
+        <v>2597</v>
       </c>
       <c r="X18">
-        <v>1440</v>
+        <v>1151</v>
       </c>
       <c r="Y18">
-        <v>0.4374240583232078</v>
+        <v>0.4432036965729688</v>
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -14955,7 +14923,7 @@
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -15032,7 +15000,7 @@
       </c>
     </row>
     <row r="21" spans="1:25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -15072,13 +15040,13 @@
         <v>0.6092619392185239</v>
       </c>
       <c r="N21">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="O21">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="P21">
-        <v>0.277027027027027</v>
+        <v>0.2775510204081633</v>
       </c>
       <c r="Q21">
         <v>126</v>
@@ -15090,26 +15058,26 @@
         <v>0.2301587301587301</v>
       </c>
       <c r="T21">
-        <v>3981</v>
+        <v>4290</v>
       </c>
       <c r="U21">
-        <v>1393</v>
+        <v>1499</v>
       </c>
       <c r="V21">
-        <v>0.349912082391359</v>
+        <v>0.3494172494172494</v>
       </c>
       <c r="W21">
-        <v>2602</v>
+        <v>2841</v>
       </c>
       <c r="X21">
-        <v>1149</v>
+        <v>1258</v>
       </c>
       <c r="Y21">
-        <v>0.4415833973866257</v>
+        <v>0.4428018303414291</v>
       </c>
     </row>
     <row r="22" spans="1:25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -15186,7 +15154,7 @@
       </c>
     </row>
     <row r="23" spans="1:25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -15263,7 +15231,7 @@
       </c>
     </row>
     <row r="24" spans="1:25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -15321,13 +15289,13 @@
         <v>0.2645161290322581</v>
       </c>
       <c r="T24">
-        <v>5294</v>
+        <v>5235</v>
       </c>
       <c r="U24">
-        <v>1779</v>
+        <v>1765</v>
       </c>
       <c r="V24">
-        <v>0.3360408009066868</v>
+        <v>0.3371537726838587</v>
       </c>
       <c r="W24">
         <v>2205</v>
@@ -15340,7 +15308,7 @@
       </c>
     </row>
     <row r="25" spans="1:25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -15417,7 +15385,7 @@
       </c>
     </row>
     <row r="26" spans="1:25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -15494,7 +15462,7 @@
       </c>
     </row>
     <row r="27" spans="1:25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -15571,7 +15539,7 @@
       </c>
     </row>
     <row r="28" spans="1:25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -15639,7 +15607,7 @@
       </c>
     </row>
     <row r="29" spans="1:25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -15716,7 +15684,7 @@
       </c>
     </row>
     <row r="30" spans="1:25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -15793,7 +15761,7 @@
       </c>
     </row>
     <row r="31" spans="1:25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -15864,7 +15832,7 @@
       </c>
     </row>
     <row r="32" spans="1:25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -15941,7 +15909,7 @@
       </c>
     </row>
     <row r="33" spans="1:25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -16018,7 +15986,7 @@
       </c>
     </row>
     <row r="34" spans="1:25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -16095,7 +16063,7 @@
       </c>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -16163,7 +16131,7 @@
       </c>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -16240,7 +16208,7 @@
       </c>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -16317,7 +16285,7 @@
       </c>
     </row>
     <row r="38" spans="1:25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -16357,22 +16325,22 @@
         <v>0.6573972099853157</v>
       </c>
       <c r="N38">
-        <v>1955</v>
+        <v>1762</v>
       </c>
       <c r="O38">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="P38">
-        <v>0.2603580562659846</v>
+        <v>0.2678774120317821</v>
       </c>
       <c r="Q38">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="R38">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="S38">
-        <v>0.8372093023255814</v>
+        <v>0.8319327731092437</v>
       </c>
       <c r="T38">
         <v>14114</v>
@@ -16394,7 +16362,7 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -16471,7 +16439,7 @@
       </c>
     </row>
     <row r="40" spans="1:25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -16548,7 +16516,7 @@
       </c>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -16625,7 +16593,7 @@
       </c>
     </row>
     <row r="42" spans="1:25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -16702,7 +16670,7 @@
       </c>
     </row>
     <row r="43" spans="1:25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -16779,7 +16747,7 @@
       </c>
     </row>
     <row r="44" spans="1:25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -16856,7 +16824,7 @@
       </c>
     </row>
     <row r="45" spans="1:25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -16924,7 +16892,7 @@
       </c>
     </row>
     <row r="46" spans="1:25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -17001,7 +16969,7 @@
       </c>
     </row>
     <row r="47" spans="1:25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -17069,7 +17037,7 @@
       </c>
     </row>
     <row r="48" spans="1:25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -17146,7 +17114,7 @@
       </c>
     </row>
     <row r="49" spans="1:25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -17223,7 +17191,7 @@
       </c>
     </row>
     <row r="50" spans="1:25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -17291,7 +17259,7 @@
       </c>
     </row>
     <row r="51" spans="1:25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -17368,7 +17336,7 @@
       </c>
     </row>
     <row r="52" spans="1:25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -17445,7 +17413,7 @@
       </c>
     </row>
     <row r="53" spans="1:25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -17523,84 +17491,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>47</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>69</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>70</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>80</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -17662,17 +17630,17 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
-        <v>3199</v>
+        <v>2983</v>
       </c>
       <c r="C3">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="D3">
-        <v>0.0665833072835261</v>
+        <v>0.06738183037210861</v>
       </c>
       <c r="E3">
         <v>1272</v>
@@ -17693,13 +17661,13 @@
         <v>0.05469783855315394</v>
       </c>
       <c r="K3">
-        <v>4471</v>
+        <v>4255</v>
       </c>
       <c r="L3">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="M3">
-        <v>0.06441511966003131</v>
+        <v>0.06486486486486487</v>
       </c>
       <c r="N3">
         <v>357</v>
@@ -17730,7 +17698,7 @@
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -17770,13 +17738,13 @@
         <v>0.06666666666666667</v>
       </c>
       <c r="N4">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O4">
         <v>2</v>
       </c>
       <c r="P4">
-        <v>0.02564102564102564</v>
+        <v>0.02597402597402598</v>
       </c>
       <c r="T4">
         <v>1356</v>
@@ -17798,7 +17766,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -17866,7 +17834,7 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -17937,7 +17905,7 @@
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -18014,7 +17982,7 @@
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -18091,7 +18059,7 @@
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -18162,7 +18130,7 @@
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -18233,7 +18201,7 @@
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -18301,7 +18269,7 @@
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -18372,7 +18340,7 @@
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -18449,7 +18417,7 @@
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -18520,7 +18488,7 @@
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -18582,7 +18550,7 @@
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -18653,7 +18621,7 @@
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -18724,78 +18692,78 @@
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>3068</v>
+        <v>2473</v>
       </c>
       <c r="C18">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="D18">
-        <v>0.04595827900912647</v>
+        <v>0.04771532551556813</v>
       </c>
       <c r="E18">
-        <v>1584</v>
+        <v>1248</v>
       </c>
       <c r="F18">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="G18">
-        <v>0.04924242424242424</v>
+        <v>0.04086538461538462</v>
       </c>
       <c r="H18">
-        <v>3048</v>
+        <v>2438</v>
       </c>
       <c r="I18">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="J18">
-        <v>0.04461942257217848</v>
+        <v>0.04142739950779328</v>
       </c>
       <c r="K18">
-        <v>4652</v>
+        <v>3721</v>
       </c>
       <c r="L18">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="M18">
-        <v>0.04707652622527945</v>
+        <v>0.04541789841440473</v>
       </c>
       <c r="N18">
-        <v>512</v>
+        <v>428</v>
       </c>
       <c r="O18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>0.017578125</v>
+        <v>0.01635514018691589</v>
       </c>
       <c r="Q18">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T18">
-        <v>7257</v>
+        <v>4996</v>
       </c>
       <c r="U18">
-        <v>678</v>
+        <v>398</v>
       </c>
       <c r="V18">
-        <v>0.09342703596527491</v>
+        <v>0.07966373098478784</v>
       </c>
       <c r="W18">
-        <v>3292</v>
+        <v>2597</v>
       </c>
       <c r="X18">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="Y18">
-        <v>0.04434993924665857</v>
+        <v>0.04582210242587601</v>
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -18866,7 +18834,7 @@
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -18937,7 +18905,7 @@
       </c>
     </row>
     <row r="21" spans="1:25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -18977,13 +18945,13 @@
         <v>0.06783646888567293</v>
       </c>
       <c r="N21">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="O21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>0.02027027027027027</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="Q21">
         <v>126</v>
@@ -18995,26 +18963,26 @@
         <v>0.007936507936507936</v>
       </c>
       <c r="T21">
-        <v>3981</v>
+        <v>4290</v>
       </c>
       <c r="U21">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="V21">
-        <v>0.1019844260236122</v>
+        <v>0.103030303030303</v>
       </c>
       <c r="W21">
-        <v>2602</v>
+        <v>2841</v>
       </c>
       <c r="X21">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Y21">
-        <v>0.06302843966179862</v>
+        <v>0.05843013023583245</v>
       </c>
     </row>
     <row r="22" spans="1:25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -19091,7 +19059,7 @@
       </c>
     </row>
     <row r="23" spans="1:25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -19162,7 +19130,7 @@
       </c>
     </row>
     <row r="24" spans="1:25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -19220,13 +19188,13 @@
         <v>0.02580645161290323</v>
       </c>
       <c r="T24">
-        <v>5294</v>
+        <v>5235</v>
       </c>
       <c r="U24">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="V24">
-        <v>0.1023800528900642</v>
+        <v>0.1033428844317097</v>
       </c>
       <c r="W24">
         <v>2205</v>
@@ -19239,7 +19207,7 @@
       </c>
     </row>
     <row r="25" spans="1:25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -19316,7 +19284,7 @@
       </c>
     </row>
     <row r="26" spans="1:25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -19381,7 +19349,7 @@
       </c>
     </row>
     <row r="27" spans="1:25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -19458,7 +19426,7 @@
       </c>
     </row>
     <row r="28" spans="1:25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -19520,7 +19488,7 @@
       </c>
     </row>
     <row r="29" spans="1:25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -19597,7 +19565,7 @@
       </c>
     </row>
     <row r="30" spans="1:25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -19674,7 +19642,7 @@
       </c>
     </row>
     <row r="31" spans="1:25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -19745,7 +19713,7 @@
       </c>
     </row>
     <row r="32" spans="1:25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -19816,7 +19784,7 @@
       </c>
     </row>
     <row r="33" spans="1:25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -19887,7 +19855,7 @@
       </c>
     </row>
     <row r="34" spans="1:25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -19964,7 +19932,7 @@
       </c>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -20026,7 +19994,7 @@
       </c>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -20097,7 +20065,7 @@
       </c>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -20168,7 +20136,7 @@
       </c>
     </row>
     <row r="38" spans="1:25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -20208,22 +20176,22 @@
         <v>0.03056167400881057</v>
       </c>
       <c r="N38">
-        <v>1955</v>
+        <v>1762</v>
       </c>
       <c r="O38">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P38">
-        <v>0.01636828644501279</v>
+        <v>0.01532349602724177</v>
       </c>
       <c r="Q38">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="R38">
         <v>1</v>
       </c>
       <c r="S38">
-        <v>0.007751937984496124</v>
+        <v>0.008403361344537815</v>
       </c>
       <c r="T38">
         <v>14114</v>
@@ -20245,7 +20213,7 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -20316,7 +20284,7 @@
       </c>
     </row>
     <row r="40" spans="1:25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -20387,7 +20355,7 @@
       </c>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -20464,7 +20432,7 @@
       </c>
     </row>
     <row r="42" spans="1:25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -20535,7 +20503,7 @@
       </c>
     </row>
     <row r="43" spans="1:25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -20612,7 +20580,7 @@
       </c>
     </row>
     <row r="44" spans="1:25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -20689,7 +20657,7 @@
       </c>
     </row>
     <row r="45" spans="1:25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -20757,7 +20725,7 @@
       </c>
     </row>
     <row r="46" spans="1:25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -20828,7 +20796,7 @@
       </c>
     </row>
     <row r="47" spans="1:25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -20890,7 +20858,7 @@
       </c>
     </row>
     <row r="48" spans="1:25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -20961,7 +20929,7 @@
       </c>
     </row>
     <row r="49" spans="1:25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -21038,7 +21006,7 @@
       </c>
     </row>
     <row r="50" spans="1:25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -21106,7 +21074,7 @@
       </c>
     </row>
     <row r="51" spans="1:25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -21177,7 +21145,7 @@
       </c>
     </row>
     <row r="52" spans="1:25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -21248,7 +21216,7 @@
       </c>
     </row>
     <row r="53" spans="1:25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -21326,84 +21294,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>49</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>60</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>61</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>71</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>72</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>82</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -21453,17 +21421,17 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
-        <v>3199</v>
+        <v>2983</v>
       </c>
       <c r="C3">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D3">
-        <v>0.01875586120662707</v>
+        <v>0.01944351324170298</v>
       </c>
       <c r="E3">
         <v>1272</v>
@@ -21484,13 +21452,13 @@
         <v>0.01146890163211292</v>
       </c>
       <c r="K3">
-        <v>4471</v>
+        <v>4255</v>
       </c>
       <c r="L3">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M3">
-        <v>0.01766942518452248</v>
+        <v>0.01809635722679201</v>
       </c>
       <c r="N3">
         <v>357</v>
@@ -21509,7 +21477,7 @@
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -21549,7 +21517,7 @@
         <v>0.002380952380952381</v>
       </c>
       <c r="N4">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T4">
         <v>1356</v>
@@ -21565,7 +21533,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -21621,7 +21589,7 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -21680,7 +21648,7 @@
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -21739,7 +21707,7 @@
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -21798,7 +21766,7 @@
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -21857,7 +21825,7 @@
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -21916,7 +21884,7 @@
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -21972,7 +21940,7 @@
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -22031,7 +21999,7 @@
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -22090,7 +22058,7 @@
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -22149,7 +22117,7 @@
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -22205,7 +22173,7 @@
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -22264,7 +22232,7 @@
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -22323,66 +22291,66 @@
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>3068</v>
+        <v>2473</v>
       </c>
       <c r="C18">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>0.005541069100391135</v>
+        <v>0.003234937323089365</v>
       </c>
       <c r="E18">
-        <v>1584</v>
+        <v>1248</v>
       </c>
       <c r="F18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G18">
-        <v>0.006313131313131313</v>
+        <v>0.005608974358974359</v>
       </c>
       <c r="H18">
-        <v>3048</v>
+        <v>2438</v>
       </c>
       <c r="I18">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J18">
-        <v>0.006233595800524934</v>
+        <v>0.005742411812961444</v>
       </c>
       <c r="K18">
-        <v>4652</v>
+        <v>3721</v>
       </c>
       <c r="L18">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="M18">
-        <v>0.005803955288048152</v>
+        <v>0.00403117441547971</v>
       </c>
       <c r="N18">
-        <v>512</v>
+        <v>428</v>
       </c>
       <c r="Q18">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T18">
-        <v>7257</v>
+        <v>4996</v>
       </c>
       <c r="W18">
-        <v>3292</v>
+        <v>2597</v>
       </c>
       <c r="X18">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Y18">
-        <v>0.005467800729040097</v>
+        <v>0.004235656526761648</v>
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -22441,7 +22409,7 @@
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -22500,7 +22468,7 @@
       </c>
     </row>
     <row r="21" spans="1:25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -22540,26 +22508,26 @@
         <v>0.01085383502170767</v>
       </c>
       <c r="N21">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="Q21">
         <v>126</v>
       </c>
       <c r="T21">
-        <v>3981</v>
+        <v>4290</v>
       </c>
       <c r="W21">
-        <v>2602</v>
+        <v>2841</v>
       </c>
       <c r="X21">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="Y21">
-        <v>0.02036894696387394</v>
+        <v>0.02111932418162619</v>
       </c>
     </row>
     <row r="22" spans="1:25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -22618,7 +22586,7 @@
       </c>
     </row>
     <row r="23" spans="1:25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -22677,7 +22645,7 @@
       </c>
     </row>
     <row r="24" spans="1:25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -22723,7 +22691,7 @@
         <v>155</v>
       </c>
       <c r="T24">
-        <v>5294</v>
+        <v>5235</v>
       </c>
       <c r="W24">
         <v>2205</v>
@@ -22736,7 +22704,7 @@
       </c>
     </row>
     <row r="25" spans="1:25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -22795,7 +22763,7 @@
       </c>
     </row>
     <row r="26" spans="1:25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -22854,7 +22822,7 @@
       </c>
     </row>
     <row r="27" spans="1:25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -22913,7 +22881,7 @@
       </c>
     </row>
     <row r="28" spans="1:25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -22963,7 +22931,7 @@
       </c>
     </row>
     <row r="29" spans="1:25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -23022,7 +22990,7 @@
       </c>
     </row>
     <row r="30" spans="1:25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -23081,7 +23049,7 @@
       </c>
     </row>
     <row r="31" spans="1:25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -23140,7 +23108,7 @@
       </c>
     </row>
     <row r="32" spans="1:25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -23199,7 +23167,7 @@
       </c>
     </row>
     <row r="33" spans="1:25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -23258,7 +23226,7 @@
       </c>
     </row>
     <row r="34" spans="1:25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -23317,7 +23285,7 @@
       </c>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -23373,7 +23341,7 @@
       </c>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -23432,7 +23400,7 @@
       </c>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -23491,7 +23459,7 @@
       </c>
     </row>
     <row r="38" spans="1:25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -23531,10 +23499,10 @@
         <v>0.00394640234948605</v>
       </c>
       <c r="N38">
-        <v>1955</v>
+        <v>1762</v>
       </c>
       <c r="Q38">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="T38">
         <v>14114</v>
@@ -23550,7 +23518,7 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -23609,7 +23577,7 @@
       </c>
     </row>
     <row r="40" spans="1:25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -23668,7 +23636,7 @@
       </c>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -23727,7 +23695,7 @@
       </c>
     </row>
     <row r="42" spans="1:25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -23786,7 +23754,7 @@
       </c>
     </row>
     <row r="43" spans="1:25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -23845,7 +23813,7 @@
       </c>
     </row>
     <row r="44" spans="1:25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -23904,7 +23872,7 @@
       </c>
     </row>
     <row r="45" spans="1:25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -23960,7 +23928,7 @@
       </c>
     </row>
     <row r="46" spans="1:25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -24019,7 +23987,7 @@
       </c>
     </row>
     <row r="47" spans="1:25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -24075,7 +24043,7 @@
       </c>
     </row>
     <row r="48" spans="1:25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -24134,7 +24102,7 @@
       </c>
     </row>
     <row r="49" spans="1:25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -24193,7 +24161,7 @@
       </c>
     </row>
     <row r="50" spans="1:25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -24243,7 +24211,7 @@
       </c>
     </row>
     <row r="51" spans="1:25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -24296,7 +24264,7 @@
       </c>
     </row>
     <row r="52" spans="1:25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -24325,7 +24293,7 @@
       </c>
     </row>
     <row r="53" spans="1:25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -24391,84 +24359,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>51</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>52</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>62</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>63</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>73</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>74</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>84</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -24536,17 +24504,17 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
-        <v>3199</v>
+        <v>2983</v>
       </c>
       <c r="C3">
-        <v>695</v>
+        <v>648</v>
       </c>
       <c r="D3">
-        <v>0.2172553923100969</v>
+        <v>0.2172309755279919</v>
       </c>
       <c r="E3">
         <v>1272</v>
@@ -24567,13 +24535,13 @@
         <v>0.2073224525805029</v>
       </c>
       <c r="K3">
-        <v>4471</v>
+        <v>4255</v>
       </c>
       <c r="L3">
-        <v>949</v>
+        <v>902</v>
       </c>
       <c r="M3">
-        <v>0.2122567658242004</v>
+        <v>0.2119858989424207</v>
       </c>
       <c r="N3">
         <v>357</v>
@@ -24604,7 +24572,7 @@
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -24644,13 +24612,13 @@
         <v>0.2666666666666667</v>
       </c>
       <c r="N4">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O4">
         <v>17</v>
       </c>
       <c r="P4">
-        <v>0.217948717948718</v>
+        <v>0.2207792207792208</v>
       </c>
       <c r="T4">
         <v>1356</v>
@@ -24672,7 +24640,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -24740,7 +24708,7 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -24817,7 +24785,7 @@
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -24894,7 +24862,7 @@
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -24971,7 +24939,7 @@
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -25048,7 +25016,7 @@
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -25125,7 +25093,7 @@
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -25193,7 +25161,7 @@
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -25270,7 +25238,7 @@
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -25347,7 +25315,7 @@
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -25424,7 +25392,7 @@
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -25492,7 +25460,7 @@
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -25569,7 +25537,7 @@
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -25646,84 +25614,78 @@
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>3068</v>
+        <v>2473</v>
       </c>
       <c r="C18">
-        <v>699</v>
+        <v>567</v>
       </c>
       <c r="D18">
-        <v>0.2278357235984355</v>
+        <v>0.2292761827739588</v>
       </c>
       <c r="E18">
-        <v>1584</v>
+        <v>1248</v>
       </c>
       <c r="F18">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="G18">
-        <v>0.2215909090909091</v>
+        <v>0.2371794871794872</v>
       </c>
       <c r="H18">
-        <v>3048</v>
+        <v>2438</v>
       </c>
       <c r="I18">
-        <v>614</v>
+        <v>511</v>
       </c>
       <c r="J18">
-        <v>0.2014435695538058</v>
+        <v>0.2095980311730927</v>
       </c>
       <c r="K18">
-        <v>4652</v>
+        <v>3721</v>
       </c>
       <c r="L18">
-        <v>1050</v>
+        <v>863</v>
       </c>
       <c r="M18">
-        <v>0.2257093723129837</v>
+        <v>0.2319269013705993</v>
       </c>
       <c r="N18">
-        <v>512</v>
+        <v>428</v>
       </c>
       <c r="O18">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="P18">
-        <v>0.330078125</v>
+        <v>0.338785046728972</v>
       </c>
       <c r="Q18">
-        <v>12</v>
-      </c>
-      <c r="R18">
-        <v>2</v>
-      </c>
-      <c r="S18">
-        <v>0.1666666666666667</v>
+        <v>4</v>
       </c>
       <c r="T18">
-        <v>7257</v>
+        <v>4996</v>
       </c>
       <c r="U18">
-        <v>2175</v>
+        <v>1520</v>
       </c>
       <c r="V18">
-        <v>0.2997106242248863</v>
+        <v>0.3042433947157726</v>
       </c>
       <c r="W18">
-        <v>3292</v>
+        <v>2597</v>
       </c>
       <c r="X18">
-        <v>749</v>
+        <v>585</v>
       </c>
       <c r="Y18">
-        <v>0.2275212636695018</v>
+        <v>0.2252599152868695</v>
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -25800,7 +25762,7 @@
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -25877,7 +25839,7 @@
       </c>
     </row>
     <row r="21" spans="1:25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -25917,13 +25879,13 @@
         <v>0.1986251808972504</v>
       </c>
       <c r="N21">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="O21">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="P21">
-        <v>0.2882882882882883</v>
+        <v>0.2918367346938776</v>
       </c>
       <c r="Q21">
         <v>126</v>
@@ -25935,26 +25897,26 @@
         <v>0.2698412698412698</v>
       </c>
       <c r="T21">
-        <v>3981</v>
+        <v>4290</v>
       </c>
       <c r="U21">
-        <v>1161</v>
+        <v>1250</v>
       </c>
       <c r="V21">
-        <v>0.2916352675207234</v>
+        <v>0.2913752913752914</v>
       </c>
       <c r="W21">
-        <v>2602</v>
+        <v>2841</v>
       </c>
       <c r="X21">
-        <v>617</v>
+        <v>670</v>
       </c>
       <c r="Y21">
-        <v>0.2371252882398155</v>
+        <v>0.2358324533614924</v>
       </c>
     </row>
     <row r="22" spans="1:25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -26031,7 +25993,7 @@
       </c>
     </row>
     <row r="23" spans="1:25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -26108,7 +26070,7 @@
       </c>
     </row>
     <row r="24" spans="1:25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -26166,13 +26128,13 @@
         <v>0.2774193548387097</v>
       </c>
       <c r="T24">
-        <v>5294</v>
+        <v>5235</v>
       </c>
       <c r="U24">
-        <v>1576</v>
+        <v>1543</v>
       </c>
       <c r="V24">
-        <v>0.297695504344541</v>
+        <v>0.2947468958930277</v>
       </c>
       <c r="W24">
         <v>2205</v>
@@ -26185,7 +26147,7 @@
       </c>
     </row>
     <row r="25" spans="1:25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -26262,7 +26224,7 @@
       </c>
     </row>
     <row r="26" spans="1:25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -26339,7 +26301,7 @@
       </c>
     </row>
     <row r="27" spans="1:25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -26416,7 +26378,7 @@
       </c>
     </row>
     <row r="28" spans="1:25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -26484,7 +26446,7 @@
       </c>
     </row>
     <row r="29" spans="1:25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -26561,7 +26523,7 @@
       </c>
     </row>
     <row r="30" spans="1:25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -26638,7 +26600,7 @@
       </c>
     </row>
     <row r="31" spans="1:25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -26715,7 +26677,7 @@
       </c>
     </row>
     <row r="32" spans="1:25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -26792,7 +26754,7 @@
       </c>
     </row>
     <row r="33" spans="1:25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -26869,7 +26831,7 @@
       </c>
     </row>
     <row r="34" spans="1:25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -26946,7 +26908,7 @@
       </c>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -27014,7 +26976,7 @@
       </c>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -27091,7 +27053,7 @@
       </c>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -27168,7 +27130,7 @@
       </c>
     </row>
     <row r="38" spans="1:25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -27208,22 +27170,22 @@
         <v>0.2100770925110132</v>
       </c>
       <c r="N38">
-        <v>1955</v>
+        <v>1762</v>
       </c>
       <c r="O38">
-        <v>597</v>
+        <v>544</v>
       </c>
       <c r="P38">
-        <v>0.3053708439897698</v>
+        <v>0.3087400681044268</v>
       </c>
       <c r="Q38">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="R38">
         <v>11</v>
       </c>
       <c r="S38">
-        <v>0.08527131782945736</v>
+        <v>0.09243697478991597</v>
       </c>
       <c r="T38">
         <v>14114</v>
@@ -27245,7 +27207,7 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -27322,7 +27284,7 @@
       </c>
     </row>
     <row r="40" spans="1:25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -27399,7 +27361,7 @@
       </c>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -27476,7 +27438,7 @@
       </c>
     </row>
     <row r="42" spans="1:25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -27553,7 +27515,7 @@
       </c>
     </row>
     <row r="43" spans="1:25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -27630,7 +27592,7 @@
       </c>
     </row>
     <row r="44" spans="1:25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -27707,7 +27669,7 @@
       </c>
     </row>
     <row r="45" spans="1:25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -27775,7 +27737,7 @@
       </c>
     </row>
     <row r="46" spans="1:25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -27852,7 +27814,7 @@
       </c>
     </row>
     <row r="47" spans="1:25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -27920,7 +27882,7 @@
       </c>
     </row>
     <row r="48" spans="1:25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -27997,7 +27959,7 @@
       </c>
     </row>
     <row r="49" spans="1:25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -28074,7 +28036,7 @@
       </c>
     </row>
     <row r="50" spans="1:25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -28142,7 +28104,7 @@
       </c>
     </row>
     <row r="51" spans="1:25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -28219,7 +28181,7 @@
       </c>
     </row>
     <row r="52" spans="1:25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -28296,7 +28258,7 @@
       </c>
     </row>
     <row r="53" spans="1:25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -28374,84 +28336,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>43</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>53</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>54</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>64</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>65</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>75</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>76</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>86</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -28519,17 +28481,17 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
-        <v>3199</v>
+        <v>2983</v>
       </c>
       <c r="C3">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="D3">
-        <v>0.08471397311659894</v>
+        <v>0.08447871270533021</v>
       </c>
       <c r="E3">
         <v>1272</v>
@@ -28550,13 +28512,13 @@
         <v>0.2179091310101456</v>
       </c>
       <c r="K3">
-        <v>4471</v>
+        <v>4255</v>
       </c>
       <c r="L3">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="M3">
-        <v>0.09885931558935361</v>
+        <v>0.09941245593419507</v>
       </c>
       <c r="N3">
         <v>357</v>
@@ -28587,7 +28549,7 @@
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -28627,13 +28589,13 @@
         <v>0.1396825396825397</v>
       </c>
       <c r="N4">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P4">
-        <v>0.5384615384615384</v>
+        <v>0.5324675324675324</v>
       </c>
       <c r="T4">
         <v>1356</v>
@@ -28655,7 +28617,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -28723,7 +28685,7 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -28800,7 +28762,7 @@
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -28877,7 +28839,7 @@
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -28954,7 +28916,7 @@
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -29025,7 +28987,7 @@
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -29102,7 +29064,7 @@
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -29170,7 +29132,7 @@
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -29247,7 +29209,7 @@
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -29324,7 +29286,7 @@
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -29401,7 +29363,7 @@
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -29469,7 +29431,7 @@
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -29546,7 +29508,7 @@
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -29623,84 +29585,84 @@
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>3068</v>
+        <v>2473</v>
       </c>
       <c r="C18">
-        <v>333</v>
+        <v>283</v>
       </c>
       <c r="D18">
-        <v>0.1085397653194263</v>
+        <v>0.1144359078042863</v>
       </c>
       <c r="E18">
-        <v>1584</v>
+        <v>1248</v>
       </c>
       <c r="F18">
-        <v>304</v>
+        <v>261</v>
       </c>
       <c r="G18">
-        <v>0.1919191919191919</v>
+        <v>0.2091346153846154</v>
       </c>
       <c r="H18">
-        <v>3048</v>
+        <v>2438</v>
       </c>
       <c r="I18">
-        <v>791</v>
+        <v>670</v>
       </c>
       <c r="J18">
-        <v>0.2595144356955381</v>
+        <v>0.2748154224774405</v>
       </c>
       <c r="K18">
-        <v>4652</v>
+        <v>3721</v>
       </c>
       <c r="L18">
-        <v>637</v>
+        <v>544</v>
       </c>
       <c r="M18">
-        <v>0.1369303525365434</v>
+        <v>0.1461972588013975</v>
       </c>
       <c r="N18">
-        <v>512</v>
+        <v>428</v>
       </c>
       <c r="O18">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="P18">
-        <v>0.45703125</v>
+        <v>0.455607476635514</v>
       </c>
       <c r="Q18">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R18">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S18">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="T18">
-        <v>7257</v>
+        <v>4996</v>
       </c>
       <c r="U18">
-        <v>2048</v>
+        <v>1489</v>
       </c>
       <c r="V18">
-        <v>0.282210279729916</v>
+        <v>0.2980384307445957</v>
       </c>
       <c r="W18">
-        <v>3292</v>
+        <v>2597</v>
       </c>
       <c r="X18">
-        <v>939</v>
+        <v>731</v>
       </c>
       <c r="Y18">
-        <v>0.2852369380315917</v>
+        <v>0.2814786291875241</v>
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -29777,7 +29739,7 @@
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -29854,7 +29816,7 @@
       </c>
     </row>
     <row r="21" spans="1:25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -29894,13 +29856,13 @@
         <v>0.1132416787264834</v>
       </c>
       <c r="N21">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="O21">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="P21">
-        <v>0.4144144144144144</v>
+        <v>0.410204081632653</v>
       </c>
       <c r="Q21">
         <v>126</v>
@@ -29912,26 +29874,26 @@
         <v>0.492063492063492</v>
       </c>
       <c r="T21">
-        <v>3981</v>
+        <v>4290</v>
       </c>
       <c r="U21">
-        <v>1021</v>
+        <v>1099</v>
       </c>
       <c r="V21">
-        <v>0.2564682240643055</v>
+        <v>0.2561771561771562</v>
       </c>
       <c r="W21">
-        <v>2602</v>
+        <v>2841</v>
       </c>
       <c r="X21">
-        <v>619</v>
+        <v>687</v>
       </c>
       <c r="Y21">
-        <v>0.2378939277478862</v>
+        <v>0.2418162618796199</v>
       </c>
     </row>
     <row r="22" spans="1:25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -30008,7 +29970,7 @@
       </c>
     </row>
     <row r="23" spans="1:25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -30085,7 +30047,7 @@
       </c>
     </row>
     <row r="24" spans="1:25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -30143,13 +30105,13 @@
         <v>0.432258064516129</v>
       </c>
       <c r="T24">
-        <v>5294</v>
+        <v>5235</v>
       </c>
       <c r="U24">
-        <v>1397</v>
+        <v>1386</v>
       </c>
       <c r="V24">
-        <v>0.263883641858708</v>
+        <v>0.264756446991404</v>
       </c>
       <c r="W24">
         <v>2205</v>
@@ -30162,7 +30124,7 @@
       </c>
     </row>
     <row r="25" spans="1:25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -30239,7 +30201,7 @@
       </c>
     </row>
     <row r="26" spans="1:25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -30316,7 +30278,7 @@
       </c>
     </row>
     <row r="27" spans="1:25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -30393,7 +30355,7 @@
       </c>
     </row>
     <row r="28" spans="1:25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -30461,7 +30423,7 @@
       </c>
     </row>
     <row r="29" spans="1:25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -30538,7 +30500,7 @@
       </c>
     </row>
     <row r="30" spans="1:25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -30615,7 +30577,7 @@
       </c>
     </row>
     <row r="31" spans="1:25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -30692,7 +30654,7 @@
       </c>
     </row>
     <row r="32" spans="1:25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -30769,7 +30731,7 @@
       </c>
     </row>
     <row r="33" spans="1:25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -30846,7 +30808,7 @@
       </c>
     </row>
     <row r="34" spans="1:25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -30923,7 +30885,7 @@
       </c>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -30991,7 +30953,7 @@
       </c>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -31068,7 +31030,7 @@
       </c>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -31145,7 +31107,7 @@
       </c>
     </row>
     <row r="38" spans="1:25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -31185,22 +31147,22 @@
         <v>0.09774229074889867</v>
       </c>
       <c r="N38">
-        <v>1955</v>
+        <v>1762</v>
       </c>
       <c r="O38">
-        <v>817</v>
+        <v>719</v>
       </c>
       <c r="P38">
-        <v>0.4179028132992327</v>
+        <v>0.4080590238365494</v>
       </c>
       <c r="Q38">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="R38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S38">
-        <v>0.06976744186046512</v>
+        <v>0.06722689075630252</v>
       </c>
       <c r="T38">
         <v>14114</v>
@@ -31222,7 +31184,7 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -31293,7 +31255,7 @@
       </c>
     </row>
     <row r="40" spans="1:25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -31370,7 +31332,7 @@
       </c>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -31447,7 +31409,7 @@
       </c>
     </row>
     <row r="42" spans="1:25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -31524,7 +31486,7 @@
       </c>
     </row>
     <row r="43" spans="1:25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -31601,7 +31563,7 @@
       </c>
     </row>
     <row r="44" spans="1:25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -31678,7 +31640,7 @@
       </c>
     </row>
     <row r="45" spans="1:25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -31746,7 +31708,7 @@
       </c>
     </row>
     <row r="46" spans="1:25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -31823,7 +31785,7 @@
       </c>
     </row>
     <row r="47" spans="1:25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -31891,7 +31853,7 @@
       </c>
     </row>
     <row r="48" spans="1:25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -31968,7 +31930,7 @@
       </c>
     </row>
     <row r="49" spans="1:25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -32045,7 +32007,7 @@
       </c>
     </row>
     <row r="50" spans="1:25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -32113,7 +32075,7 @@
       </c>
     </row>
     <row r="51" spans="1:25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -32190,7 +32152,7 @@
       </c>
     </row>
     <row r="52" spans="1:25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -32267,7 +32229,7 @@
       </c>
     </row>
     <row r="53" spans="1:25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
